--- a/inquiry_forms/025_mentorship_membership_pricing_inquiry--inquiry_forms.xlsx
+++ b/inquiry_forms/025_mentorship_membership_pricing_inquiry--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Premium'}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'ultimate'}</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Ultimate'}</t>
+          <t>Ultimate</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>value:ประก</t>
+          <t>valueประก</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>value:ประก</t>
+          <t>valueประก</t>
         </is>
       </c>
     </row>
@@ -968,29 +968,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>valueประก</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>valueประก</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_much_energy_choices</t>
+          <t>preferred_mentor_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>tier_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'high'}</t>
+          <t>Tier 1</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'tier_1'}</t>
+          <t>tier_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Tier 1'}</t>
+          <t>Tier 2</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'tier_2'}</t>
+          <t>tier_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Tier 2'}</t>
+          <t>Tier 3</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'tier_3'}</t>
+          <t>tier_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Tier 3'}</t>
+          <t>Tier 4</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'tier_4'}</t>
+          <t>value:ประก</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Tier 4'}</t>
+          <t>value:ประก</t>
         </is>
       </c>
     </row>
@@ -1070,29 +1070,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>value:ประก</t>
+          <t>tier_6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>value:ประก</t>
+          <t>Tier 6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>preferred_mentor_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'tier_6'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Tier 6'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>video_call</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Video call</t>
         </is>
       </c>
     </row>
@@ -1138,29 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'video_call'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Video call'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'in-person'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
